--- a/deploy/084_ENT_TENENCIA_PRECIO/74 TENENCIA_PRECIO.xlsx
+++ b/deploy/084_ENT_TENENCIA_PRECIO/74 TENENCIA_PRECIO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\deploy\084_ENT_TENENCIA_PRECIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A76B5F6D-0CD2-4B91-BC9C-097A97C00FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23B0951-A4C5-477C-94A8-7653873073A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1890" yWindow="8400" windowWidth="21830" windowHeight="13000" xr2:uid="{B1155225-DE4F-4A57-900D-C92D9AEA4A77}"/>
+    <workbookView xWindow="1000" yWindow="4630" windowWidth="24350" windowHeight="11090" xr2:uid="{B1155225-DE4F-4A57-900D-C92D9AEA4A77}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>TITULOOBJETO</t>
   </si>
@@ -110,25 +110,16 @@
     <t>RP</t>
   </si>
   <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>CR</t>
-  </si>
-  <si>
-    <t>BCIADMO</t>
-  </si>
-  <si>
-    <t>BP0001M</t>
-  </si>
-  <si>
-    <t>BP0001W</t>
-  </si>
-  <si>
-    <t>BP0002M</t>
-  </si>
-  <si>
-    <t>BP0003M</t>
+    <t>000111</t>
+  </si>
+  <si>
+    <t>000750</t>
+  </si>
+  <si>
+    <t>000760</t>
+  </si>
+  <si>
+    <t>000770</t>
   </si>
 </sst>
 </file>
@@ -164,9 +155,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -501,8 +493,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16FA4ED-6584-4027-BBC3-285FEFD31209}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -552,14 +557,14 @@
       <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="E2">
-        <v>111</v>
+      <c r="E2" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2">
-        <v>750</v>
+      <c r="G2" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="H2">
         <v>5000</v>
@@ -587,14 +592,14 @@
       <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="E3">
-        <v>750</v>
+      <c r="E3" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>760</v>
+      <c r="G3" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="H3">
         <v>3000</v>
@@ -622,14 +627,14 @@
       <c r="D4" t="s">
         <v>19</v>
       </c>
-      <c r="E4">
-        <v>760</v>
+      <c r="E4" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4">
-        <v>111</v>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="H4">
         <v>8000</v>
@@ -657,14 +662,14 @@
       <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="E5">
-        <v>770</v>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5">
-        <v>775</v>
+      <c r="G5" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="H5">
         <v>2000</v>
@@ -677,216 +682,6 @@
       </c>
       <c r="K5" s="1">
         <v>46190</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
-        <v>0.65432100000000004</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6">
-        <v>775</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>111</v>
-      </c>
-      <c r="H6">
-        <v>10000</v>
-      </c>
-      <c r="I6">
-        <v>2000</v>
-      </c>
-      <c r="J6">
-        <v>800</v>
-      </c>
-      <c r="K6" s="1">
-        <v>46190</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7">
-        <v>102.33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>111</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>750</v>
-      </c>
-      <c r="H7">
-        <v>1500</v>
-      </c>
-      <c r="I7">
-        <v>300</v>
-      </c>
-      <c r="J7">
-        <v>200</v>
-      </c>
-      <c r="K7" s="1">
-        <v>46191</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8">
-        <v>99.876543209999994</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8">
-        <v>750</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>760</v>
-      </c>
-      <c r="H8">
-        <v>6000</v>
-      </c>
-      <c r="I8">
-        <v>1200</v>
-      </c>
-      <c r="J8">
-        <v>400</v>
-      </c>
-      <c r="K8" s="1">
-        <v>46191</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9">
-        <v>100.123</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9">
-        <v>760</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>111</v>
-      </c>
-      <c r="H9">
-        <v>4000</v>
-      </c>
-      <c r="I9">
-        <v>800</v>
-      </c>
-      <c r="J9">
-        <v>600</v>
-      </c>
-      <c r="K9" s="1">
-        <v>46191</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10">
-        <v>97.555555549999994</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10">
-        <v>770</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>775</v>
-      </c>
-      <c r="H10">
-        <v>7000</v>
-      </c>
-      <c r="I10">
-        <v>1500</v>
-      </c>
-      <c r="J10">
-        <v>900</v>
-      </c>
-      <c r="K10" s="1">
-        <v>46192</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11">
-        <v>101.00000000999999</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11">
-        <v>775</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>111</v>
-      </c>
-      <c r="H11">
-        <v>2500</v>
-      </c>
-      <c r="I11">
-        <v>400</v>
-      </c>
-      <c r="J11">
-        <v>150</v>
-      </c>
-      <c r="K11" s="1">
-        <v>46192</v>
       </c>
     </row>
   </sheetData>
